--- a/public/exports/29189978.xlsx
+++ b/public/exports/29189978.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">374028, 374029</t>
+          <t xml:space="preserve">353477, 353478</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>712</v>
+        <v>815</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4117377</t>
+          <t xml:space="preserve">361636</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F12">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141177</t>
+          <t xml:space="preserve">361636, 361638, 361639</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F13">
-        <v>3262</v>
+        <v>323</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">374028, 374029</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>441</v>
+        <v>712</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">375845, 375846, 375847, 375848</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>441</v>
+        <v>1260</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151141</t>
+          <t xml:space="preserve">375855, 375856</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>333</v>
+        <v>666</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">4117377</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F17">
-        <v>580</v>
+        <v>300</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">4141177</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F18">
-        <v>1267</v>
+        <v>3262</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173780</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F19">
-        <v>1130</v>
+        <v>441</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F20">
-        <v>2569</v>
+        <v>441</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4174148</t>
+          <t xml:space="preserve">4151141</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F21">
-        <v>1225</v>
+        <v>333</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617299</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F22">
-        <v>439</v>
+        <v>580</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617326</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F23">
-        <v>374</v>
+        <v>1267</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617732</t>
+          <t xml:space="preserve">4173780</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F24">
-        <v>330</v>
+        <v>1130</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618905</t>
+          <t xml:space="preserve">4174148</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>416</v>
+        <v>1225</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619162</t>
+          <t xml:space="preserve">5617299</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F26">
-        <v>584</v>
+        <v>439</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619216</t>
+          <t xml:space="preserve">5617326</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F27">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">741584, 5619151</t>
+          <t xml:space="preserve">5617732</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>865</v>
+        <v>330</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">741593, 10136366</t>
+          <t xml:space="preserve">5618905</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F29">
-        <v>253</v>
+        <v>416</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">741594, 9787579</t>
+          <t xml:space="preserve">5619162</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>500</v>
+        <v>584</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">741623, 5617339</t>
+          <t xml:space="preserve">5619216</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">741623, 5617339</t>
+          <t xml:space="preserve">741593, 10136366</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F32">
-        <v>1142</v>
+        <v>253</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">741623, 5617339</t>
+          <t xml:space="preserve">741594, 9787579</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F33">
-        <v>1930</v>
+        <v>500</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">741658, 10136366</t>
+          <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>358</v>
+        <v>320</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">741660, 100168061</t>
+          <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F35">
-        <v>833</v>
+        <v>1142</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">741661, 4174515</t>
+          <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F36">
-        <v>550</v>
+        <v>1930</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">741662, 4123842</t>
+          <t xml:space="preserve">741658, 10136366</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F37">
-        <v>401</v>
+        <v>358</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">741663, 4123842</t>
+          <t xml:space="preserve">741660, 100168061</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>1540</v>
+        <v>833</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">741674, 4126345</t>
+          <t xml:space="preserve">741661, 4174515</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F39">
-        <v>1893</v>
+        <v>550</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">741676, 4123019</t>
+          <t xml:space="preserve">741662, 4123842</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F40">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">741663, 4123842</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F41">
-        <v>1160</v>
+        <v>1540</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">741674, 4126345</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F42">
-        <v>393</v>
+        <v>1893</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">741676, 4123019</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>737</v>
+        <v>425</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100016008</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F56">
-        <v>551</v>
+        <v>2569</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311002109</t>
+          <t xml:space="preserve">200041449</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-05</t>
+          <t xml:space="preserve">2020-11-21</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064534</t>
+          <t xml:space="preserve">741584, 5619151</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F57">
-        <v>625</v>
+        <v>865</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311088576</t>
+          <t xml:space="preserve">200047752</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-17</t>
+          <t xml:space="preserve">2021-04-07</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123748</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,26 +2890,26 @@
         </is>
       </c>
       <c r="F58">
-        <v>1763</v>
+        <v>1160</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199997</t>
+          <t xml:space="preserve">310034752</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">361636</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,26 +2940,26 @@
         </is>
       </c>
       <c r="F59">
-        <v>258</v>
+        <v>393</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212799</t>
+          <t xml:space="preserve">310034752</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">361636, 361638, 361639</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2990,26 +2990,26 @@
         </is>
       </c>
       <c r="F60">
-        <v>323</v>
+        <v>737</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212802</t>
+          <t xml:space="preserve">310034752</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618905</t>
+          <t xml:space="preserve">100016008</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,26 +3040,26 @@
         </is>
       </c>
       <c r="F61">
-        <v>606</v>
+        <v>551</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212792</t>
+          <t xml:space="preserve">311002109</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8034374</t>
+          <t xml:space="preserve">100064534</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,26 +3090,26 @@
         </is>
       </c>
       <c r="F62">
-        <v>461</v>
+        <v>625</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212953</t>
+          <t xml:space="preserve">311088576</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2024-12-17</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8587307</t>
+          <t xml:space="preserve">4123748</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="F63">
-        <v>445</v>
+        <v>1763</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215580</t>
+          <t xml:space="preserve">311199997</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-01</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124588</t>
+          <t xml:space="preserve">5618905</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="F64">
-        <v>364</v>
+        <v>606</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216521</t>
+          <t xml:space="preserve">311212792</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-07</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4125011</t>
+          <t xml:space="preserve">8034374</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="F65">
-        <v>605</v>
+        <v>461</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216854</t>
+          <t xml:space="preserve">311212953</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148336</t>
+          <t xml:space="preserve">8587307</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="F66">
-        <v>757</v>
+        <v>445</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218178</t>
+          <t xml:space="preserve">311215580</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123772</t>
+          <t xml:space="preserve">4124588</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>445</v>
+        <v>364</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219438</t>
+          <t xml:space="preserve">311216521</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2026-12-07</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148280</t>
+          <t xml:space="preserve">4125011</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="F68">
-        <v>521</v>
+        <v>605</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219420</t>
+          <t xml:space="preserve">311216854</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7811024</t>
+          <t xml:space="preserve">4148336</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>492</v>
+        <v>757</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219423</t>
+          <t xml:space="preserve">311218178</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9516512</t>
+          <t xml:space="preserve">4123772</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,11 +3490,11 @@
         </is>
       </c>
       <c r="F70">
-        <v>529</v>
+        <v>445</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219452</t>
+          <t xml:space="preserve">311219438</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155496</t>
+          <t xml:space="preserve">4148280</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,16 +3540,16 @@
         </is>
       </c>
       <c r="F71">
-        <v>353</v>
+        <v>521</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231282</t>
+          <t xml:space="preserve">311219420</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-01</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4149074</t>
+          <t xml:space="preserve">7811024</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>389</v>
+        <v>492</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249201</t>
+          <t xml:space="preserve">311219423</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618867</t>
+          <t xml:space="preserve">9516512</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>769</v>
+        <v>529</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250893</t>
+          <t xml:space="preserve">311219452</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173991</t>
+          <t xml:space="preserve">4155496</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="F74">
-        <v>6272</v>
+        <v>353</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253826</t>
+          <t xml:space="preserve">311231282</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-14</t>
+          <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173991</t>
+          <t xml:space="preserve">4149074</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F75">
-        <v>787</v>
+        <v>389</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253826</t>
+          <t xml:space="preserve">311249201</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-14</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618735</t>
+          <t xml:space="preserve">5618867</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>672</v>
+        <v>769</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253843</t>
+          <t xml:space="preserve">311250893</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-14</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,20 +3831,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926304</t>
+          <t xml:space="preserve">4173991</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>1282</v>
+        <v>6272</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253876</t>
+          <t xml:space="preserve">311253826</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3881,20 +3881,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926307</t>
+          <t xml:space="preserve">4173991</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F78">
-        <v>2200</v>
+        <v>787</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253872</t>
+          <t xml:space="preserve">311253826</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148297</t>
+          <t xml:space="preserve">5618735</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="F79">
-        <v>1174</v>
+        <v>672</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254476</t>
+          <t xml:space="preserve">311253843</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148190</t>
+          <t xml:space="preserve">9926304</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>1095</v>
+        <v>1282</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255745</t>
+          <t xml:space="preserve">311253876</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148190</t>
+          <t xml:space="preserve">9926307</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>338</v>
+        <v>2200</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255745</t>
+          <t xml:space="preserve">311253872</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148947</t>
+          <t xml:space="preserve">4148297</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>715</v>
+        <v>1174</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258642</t>
+          <t xml:space="preserve">311254476</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617299</t>
+          <t xml:space="preserve">4148947</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="F83">
-        <v>628</v>
+        <v>715</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258644</t>
+          <t xml:space="preserve">311258642</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617697</t>
+          <t xml:space="preserve">5617299</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,11 +4190,11 @@
         </is>
       </c>
       <c r="F84">
-        <v>1675</v>
+        <v>628</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258643</t>
+          <t xml:space="preserve">311258644</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123336</t>
+          <t xml:space="preserve">5617697</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="F85">
-        <v>970</v>
+        <v>1675</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258741</t>
+          <t xml:space="preserve">311258643</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151345</t>
+          <t xml:space="preserve">4123336</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F86">
-        <v>851</v>
+        <v>970</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258719</t>
+          <t xml:space="preserve">311258741</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4149546</t>
+          <t xml:space="preserve">4151345</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>275</v>
+        <v>851</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280697</t>
+          <t xml:space="preserve">311258719</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-26</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">4149546</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,16 +4390,16 @@
         </is>
       </c>
       <c r="F88">
-        <v>5211</v>
+        <v>275</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287373</t>
+          <t xml:space="preserve">311280697</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-10-26</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617328</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="F89">
-        <v>722</v>
+        <v>5211</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291350</t>
+          <t xml:space="preserve">311287373</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617696</t>
+          <t xml:space="preserve">5617328</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>6275</v>
+        <v>722</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291465</t>
+          <t xml:space="preserve">311291350</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-07</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4581,20 +4581,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803816</t>
+          <t xml:space="preserve">4148745</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F92">
-        <v>360</v>
+        <v>3923</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294461</t>
+          <t xml:space="preserve">311294457</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124915</t>
+          <t xml:space="preserve">4155954</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>2812</v>
+        <v>576</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294474</t>
+          <t xml:space="preserve">311294468</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4681,20 +4681,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148745</t>
+          <t xml:space="preserve">4155954</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F94">
-        <v>3923</v>
+        <v>2481</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294457</t>
+          <t xml:space="preserve">311294468</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4736,15 +4736,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F95">
-        <v>576</v>
+        <v>1214</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294468</t>
+          <t xml:space="preserve">311294470</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4786,11 +4786,11 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F96">
-        <v>2481</v>
+        <v>365</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155954</t>
+          <t xml:space="preserve">5617617</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F97">
-        <v>1214</v>
+        <v>7166</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294471</t>
+          <t xml:space="preserve">311294654</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-25</t>
+          <t xml:space="preserve">2028-01-26</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155954</t>
+          <t xml:space="preserve">4152244</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F98">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294468</t>
+          <t xml:space="preserve">311296508</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-25</t>
+          <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617617</t>
+          <t xml:space="preserve">4152244</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F99">
-        <v>7166</v>
+        <v>463</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294654</t>
+          <t xml:space="preserve">311296508</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-26</t>
+          <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4986,11 +4986,11 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F100">
-        <v>403</v>
+        <v>253</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5031,20 +5031,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4152244</t>
+          <t xml:space="preserve">8124496</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F101">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296508</t>
+          <t xml:space="preserve">311296510</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4152244</t>
+          <t xml:space="preserve">8124496</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F102">
-        <v>253</v>
+        <v>490</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296508</t>
+          <t xml:space="preserve">311296510</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5131,20 +5131,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124496</t>
+          <t xml:space="preserve">8708462</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F103">
-        <v>490</v>
+        <v>1466</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296510</t>
+          <t xml:space="preserve">311296511</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124496</t>
+          <t xml:space="preserve">4141159</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>490</v>
+        <v>2122</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296510</t>
+          <t xml:space="preserve">311299126</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-07</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708462</t>
+          <t xml:space="preserve">4141159</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F105">
-        <v>1466</v>
+        <v>640</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296511</t>
+          <t xml:space="preserve">311299126</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-07</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5286,11 +5286,11 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
-        <v>2122</v>
+        <v>2258</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5336,11 +5336,11 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F107">
-        <v>640</v>
+        <v>3414</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5386,11 +5386,11 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F108">
-        <v>2258</v>
+        <v>703</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5436,11 +5436,11 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F109">
-        <v>3414</v>
+        <v>691</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141159</t>
+          <t xml:space="preserve">4151491</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F110">
-        <v>703</v>
+        <v>865</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299126</t>
+          <t xml:space="preserve">311330686</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141159</t>
+          <t xml:space="preserve">5618817</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>691</v>
+        <v>1294</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299126</t>
+          <t xml:space="preserve">311332828</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-08-28</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151491</t>
+          <t xml:space="preserve">4124942</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>865</v>
+        <v>430</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330686</t>
+          <t xml:space="preserve">311339459</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-15</t>
+          <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618817</t>
+          <t xml:space="preserve">5618414</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>1294</v>
+        <v>9380</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332828</t>
+          <t xml:space="preserve">311339427</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-28</t>
+          <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124942</t>
+          <t xml:space="preserve">7205819</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="F114">
-        <v>430</v>
+        <v>2019</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339459</t>
+          <t xml:space="preserve">311340763</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-03</t>
+          <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618414</t>
+          <t xml:space="preserve">7205819</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>9380</v>
+        <v>6224</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339427</t>
+          <t xml:space="preserve">311340762</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-03</t>
+          <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205819</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F116">
-        <v>2019</v>
+        <v>875</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340763</t>
+          <t xml:space="preserve">311344086</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-10</t>
+          <t xml:space="preserve">2028-10-30</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205819</t>
+          <t xml:space="preserve">4165334</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>6224</v>
+        <v>4960</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340762</t>
+          <t xml:space="preserve">311347460</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-10</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4165334</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F118">
-        <v>875</v>
+        <v>779</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344086</t>
+          <t xml:space="preserve">311347460</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-30</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165334</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5940,16 +5940,16 @@
         </is>
       </c>
       <c r="F119">
-        <v>4960</v>
+        <v>480</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347460</t>
+          <t xml:space="preserve">311352227</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165334</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="F120">
-        <v>779</v>
+        <v>523</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347460</t>
+          <t xml:space="preserve">311352227</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>480</v>
+        <v>2790</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352227</t>
+          <t xml:space="preserve">311354232</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>523</v>
+        <v>2973</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352227</t>
+          <t xml:space="preserve">311354232</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,16 +6140,16 @@
         </is>
       </c>
       <c r="F123">
-        <v>2790</v>
+        <v>3597</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354232</t>
+          <t xml:space="preserve">311358653</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-10</t>
+          <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F124">
-        <v>2973</v>
+        <v>4680</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354232</t>
+          <t xml:space="preserve">311358653</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-10</t>
+          <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6236,11 +6236,11 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F125">
-        <v>3597</v>
+        <v>667</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6286,15 +6286,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F126">
-        <v>4680</v>
+        <v>488</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358653</t>
+          <t xml:space="preserve">311358656</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F127">
-        <v>667</v>
+        <v>872</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F128">
-        <v>488</v>
+        <v>1068</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358656</t>
+          <t xml:space="preserve">311364664</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-08</t>
+          <t xml:space="preserve">2029-03-14</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F129">
-        <v>872</v>
+        <v>1052</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358653</t>
+          <t xml:space="preserve">311364992</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-08</t>
+          <t xml:space="preserve">2029-03-15</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">4148190</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>1068</v>
+        <v>1095</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311364664</t>
+          <t xml:space="preserve">311377157</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-14</t>
+          <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">4148190</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F131">
-        <v>1052</v>
+        <v>338</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311364992</t>
+          <t xml:space="preserve">311377157</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-15</t>
+          <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">353477, 353478</t>
+          <t xml:space="preserve">4124915</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F134">
-        <v>815</v>
+        <v>2812</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311413537</t>
+          <t xml:space="preserve">311417162</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-12</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618818</t>
+          <t xml:space="preserve">1803816</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F135">
-        <v>1422</v>
+        <v>360</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418867</t>
+          <t xml:space="preserve">311417751</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-01-17</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8496559</t>
+          <t xml:space="preserve">5618818</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>728</v>
+        <v>1422</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419346</t>
+          <t xml:space="preserve">311418867</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-28</t>
+          <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">8496559</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>453</v>
+        <v>728</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420126</t>
+          <t xml:space="preserve">311419346</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-01-28</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961824</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="F138">
-        <v>725</v>
+        <v>453</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420125</t>
+          <t xml:space="preserve">311420126</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708462</t>
+          <t xml:space="preserve">7961824</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>480</v>
+        <v>725</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422782</t>
+          <t xml:space="preserve">311420125</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-14</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7216054</t>
+          <t xml:space="preserve">8708462</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F140">
-        <v>3084</v>
+        <v>480</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424218</t>
+          <t xml:space="preserve">311422782</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-02-14</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7036,15 +7036,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F141">
-        <v>1923</v>
+        <v>3084</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311434528</t>
+          <t xml:space="preserve">311424218</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151141</t>
+          <t xml:space="preserve">7216054</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F142">
-        <v>2309</v>
+        <v>1923</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448357</t>
+          <t xml:space="preserve">311434528</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-07</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7136,11 +7136,11 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143">
-        <v>583</v>
+        <v>2309</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7186,11 +7186,11 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F144">
-        <v>996</v>
+        <v>583</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7236,11 +7236,11 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F145">
-        <v>960</v>
+        <v>996</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141859</t>
+          <t xml:space="preserve">4151141</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F146">
-        <v>262</v>
+        <v>960</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454198</t>
+          <t xml:space="preserve">311448357</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-13</t>
+          <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F147">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F148">
@@ -7436,15 +7436,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F149">
-        <v>357</v>
+        <v>262</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454196</t>
+          <t xml:space="preserve">311454198</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7486,15 +7486,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F150">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454197</t>
+          <t xml:space="preserve">311454196</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141547</t>
+          <t xml:space="preserve">4141859</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F151">
-        <v>4455</v>
+        <v>369</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476580</t>
+          <t xml:space="preserve">311454197</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-18</t>
+          <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">375855, 375856</t>
+          <t xml:space="preserve">4141547</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F152">
-        <v>666</v>
+        <v>4455</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551602</t>
+          <t xml:space="preserve">311476580</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-29</t>
+          <t xml:space="preserve">2030-11-18</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">375845, 375846, 375847, 375848</t>
+          <t xml:space="preserve">5617696</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7840,16 +7840,16 @@
         </is>
       </c>
       <c r="F157">
-        <v>1260</v>
+        <v>6275</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561556</t>
+          <t xml:space="preserve">311630904</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-12</t>
+          <t xml:space="preserve">2032-09-26</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">

--- a/public/exports/29189978.xlsx
+++ b/public/exports/29189978.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:L164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marienhoffvej 13D</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100168061</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>699</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marienhoffvej 13B</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100168061</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>2103</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandballevej 5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">10033354</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>274</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rodskovvej 58</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">100465851</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1030</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">100625342</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>804</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 4A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">101001610, 101001611</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>4075</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestervej 15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">10136366</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>376</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestervej 17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">10136366</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>547</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestervej 19</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">10136366</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>450</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lindebo 1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">353477, 353478</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>815</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">361636</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>258</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 10</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">361636, 361638, 361639</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>323</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ebdrupvej 10A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">374028, 374029</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>712</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørreport 2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">375845, 375846, 375847, 375848</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>1260</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkegade 30A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">375855, 375856</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>666</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pollen 2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">4117377</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>300</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skrejrupvej 9B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141177</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">23</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>3262</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>441</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>441</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151141</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>333</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bispemosevej 5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8444</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173743</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>580</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bispemosevej 5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8444</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173743</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1267</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173780</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>1130</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">4174148</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>1225</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 8</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617299</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>439</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">S.A. Jensens Vej 3</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617326</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>374</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørrealle 4B</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617732</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>330</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egedalsvej 11</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618905</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>416</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Falcksvej 4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">5619162</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>584</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Falcksvej 1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">5619216</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>397</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stockflethsvej 13B</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">741593, 10136366</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>253</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stockflethsvej 12</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">741594, 9787579</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>500</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">S.A. Jensens Vej 4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>320</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">S.A. Jensens Vej 4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>1142</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">S.A. Jensens Vej 4</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1930</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skudehavnen 2B</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">741658, 10136366</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>358</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marienhoffvej 13C</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">741660, 100168061</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>833</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ebdrupvej 1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">741661, 4174515</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>550</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brunmosevej 3B</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">741662, 4123842</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>401</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brunmosevej 3C</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">741663, 4123842</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>1540</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalen 2B</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">741674, 4126345</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>1893</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovbakkevej 15</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">741676, 4123019</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>425</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>766</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 25</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">7811024</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>254</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lyngevej 7O</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">8124496</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>490</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 12</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">8587308</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>1111</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egedalsvej 3</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">8708759</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>264</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrivej 21</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">8925031</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1047</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gråskegårdevej 2B</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">9154991</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>948</v>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Amaliegårdvej 23</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">9858040</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>260</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ågårdvej 2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">9888746</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>309</v>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bagvænget 12</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">9926307</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>769</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dråbyvej 9</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">9766554</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>265</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">100132095</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbakken 9</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141141</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>633</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">200020792</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 33</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173793</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>2569</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">200041449</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-11-21</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovalleen 1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">741584, 5619151</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>865</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">200047752</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-04-07</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>1160</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">310034752</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>393</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">310034752</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Drosselvej 1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>737</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">310034752</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tendrup Hovvej 7A</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">100016008</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>551</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311002109</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østeralle 33</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">100064534</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>625</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311088576</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-12-17</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">4123748</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>1763</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311199997</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egedalsvej 7</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618905</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>606</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311212792</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hyrdebakken 2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">8034374</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>461</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311212953</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moesbakken 2A</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">8587307</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>445</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311215580</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-01</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Poppelvej 9</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">4124588</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>364</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311216521</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-07</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordre Ringvej 5</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">4125011</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>605</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311216854</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Falcksvej 2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148336</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>757</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311218178</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bøgevej 1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">4123772</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>445</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311219438</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Eskerodvej 5</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148280</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>521</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311219420</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 25</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">7811024</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>492</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311219423</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ågårdvej 3</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">9516512</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>529</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311219452</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dalgårdsvej 2A</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">4155496</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>353</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311231282</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alpedalen 14</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">4149074</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>389</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311249201</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egedalsvej 2</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618867</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>769</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311250893</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 27</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173991</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>6272</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311253826</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 27</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173991</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>787</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311253826</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandgårdshøj 46A</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618735</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>672</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311253843</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestervej 7</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">9926304</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>1282</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311253876</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bagvænget 12</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">9926307</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>2200</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311253872</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rosenholmvej 1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148297</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>1174</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311254476</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nyvej 3</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148947</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>715</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311258642</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandvejen 8</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617299</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>628</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311258644</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østeralle 17A</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617697</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>1675</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311258643</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 116A</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">4123336</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>970</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311258741</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mosevej 9</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151345</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>851</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311258719</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 24A</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">4149546</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>275</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311280697</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-26</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bispemosevej 5</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8444</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173743</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>5211</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311287373</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">S.A. Jensens Vej 1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617328</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>722</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311291350</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Maarupvej 3</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">4174157</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>1503</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311293050</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tingvej 17</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148745</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>3923</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311294457</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kløvervangen 6A</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">4155954</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>576</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311294468</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kløvervangen 6A</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">4155954</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>2481</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311294468</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kløvervangen 6B</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">4155954</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>1214</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311294470</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kløvervangen 6A</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">4155954</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>365</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311294468</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 7</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617617</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>7166</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311294654</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-26</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Århusvej 27</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">4152244</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>403</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311296508</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Århusvej 27</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">4152244</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>463</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311296508</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Århusvej 27</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">4152244</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>253</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311296508</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lyngevej 7</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">8124496</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>490</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311296510</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lyngevej 7H</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">8124496</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>490</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311296510</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lyngevej 3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">8708462</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>1466</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311296511</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skrejrupvej 1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141159</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>2122</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311299126</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skrejrupvej 1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141159</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>640</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311299126</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skrejrupvej 1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141159</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>2258</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311299126</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skrejrupvej 1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141159</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>3414</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311299126</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skrejrupvej 1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141159</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>703</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">311299126</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skrejrupvej 7</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141159</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>691</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311299126</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 19</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151491</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>865</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">311330686</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørreport 18A</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618817</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>1294</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t xml:space="preserve">311332828</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-08-28</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordre Ringvej 7A</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">4124942</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>430</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311339459</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundbergsvej 2</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618414</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>9380</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311339427</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rosengården 1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">7205819</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>2019</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311340763</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5731,33 +6871,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rosengården 1</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">7205819</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>6224</v>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311340762</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
+      <c r="I115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311340765</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5781,33 +6931,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kløvevej 1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">4126345</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="H116">
         <v>875</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">311344086</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-10-30</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5831,33 +6991,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skoletoften 17</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">4165334</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>4960</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">311347460</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5881,33 +7051,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skoletoften 17</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">4165334</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>779</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">311347460</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5931,33 +7111,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 29</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173793</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>480</v>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">311352227</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5981,33 +7171,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 29</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173793</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F120">
+      <c r="H120">
         <v>523</v>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">311352227</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6031,33 +7231,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalen 2</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t xml:space="preserve">4126345</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F121">
+      <c r="H121">
         <v>2790</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t xml:space="preserve">311354232</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6081,33 +7291,43 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalen 2</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t xml:space="preserve">4126345</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F122">
+      <c r="H122">
         <v>2973</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t xml:space="preserve">311354232</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6131,33 +7351,43 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F123">
+      <c r="H123">
         <v>3597</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="I123" t="inlineStr">
         <is>
           <t xml:space="preserve">311358653</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="J123" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
+      <c r="K123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6181,33 +7411,43 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F124">
+      <c r="H124">
         <v>4680</v>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">311358653</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
+      <c r="K124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6231,33 +7471,43 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F125">
+      <c r="H125">
         <v>667</v>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">311358653</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6281,33 +7531,43 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevangen 1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F126">
+      <c r="H126">
         <v>488</v>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t xml:space="preserve">311358656</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
+      <c r="K126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6331,33 +7591,43 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F127">
+      <c r="H127">
         <v>872</v>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t xml:space="preserve">311358653</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
+      <c r="K127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6381,33 +7651,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 41</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173832</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F128">
+      <c r="H128">
         <v>1068</v>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t xml:space="preserve">311364664</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-03-14</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6431,33 +7711,43 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 39</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173832</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F129">
+      <c r="H129">
         <v>1052</v>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t xml:space="preserve">311364992</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-03-15</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6481,33 +7771,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rodskovvej 10A</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148190</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F130">
+      <c r="H130">
         <v>1095</v>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t xml:space="preserve">311377157</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
+      <c r="K130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6531,33 +7831,43 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rodskovvej 10B</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148190</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F131">
+      <c r="H131">
         <v>338</v>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t xml:space="preserve">311377157</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="J131" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
+      <c r="K131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6581,33 +7891,43 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Marienhoffvej 11A</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t xml:space="preserve">1447910</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F132">
+      <c r="H132">
         <v>5629</v>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t xml:space="preserve">311412947</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-09</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6631,33 +7951,43 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lufthavnsvej 17</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t xml:space="preserve">4171414</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F133">
+      <c r="H133">
         <v>464</v>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t xml:space="preserve">311413089</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-10</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6681,33 +8011,43 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nordre Ringvej 9K</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8550</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t xml:space="preserve">4124915</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F134">
+      <c r="H134">
         <v>2812</v>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">311417162</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
+      <c r="K134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6731,33 +8071,43 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Århusvej 33H</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t xml:space="preserve">1803816</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F135">
+      <c r="H135">
         <v>360</v>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t xml:space="preserve">311417751</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-01-17</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
+      <c r="K135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6781,33 +8131,43 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bakkevej 5A</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618818</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F136">
+      <c r="H136">
         <v>1422</v>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="I136" t="inlineStr">
         <is>
           <t xml:space="preserve">311418867</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
+      <c r="K136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6831,33 +8191,43 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørreport 20A</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t xml:space="preserve">8496559</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F137">
+      <c r="H137">
         <v>728</v>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t xml:space="preserve">311419346</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-01-28</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
+      <c r="K137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6881,33 +8251,43 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 37</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173832</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F138">
+      <c r="H138">
         <v>453</v>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t xml:space="preserve">311420126</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
+      <c r="K138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6931,33 +8311,43 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bugtrupvej 35A</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8560</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t xml:space="preserve">7961824</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F139">
+      <c r="H139">
         <v>725</v>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t xml:space="preserve">311420125</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
+      <c r="K139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6981,33 +8371,43 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lyngevej 5R</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8420</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t xml:space="preserve">8708462</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F140">
+      <c r="H140">
         <v>480</v>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t xml:space="preserve">311422782</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-02-14</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
+      <c r="K140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7031,33 +8431,43 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 77</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t xml:space="preserve">7216054</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F141">
+      <c r="H141">
         <v>3084</v>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t xml:space="preserve">311424218</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
+      <c r="K141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7081,33 +8491,43 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 75A</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t xml:space="preserve">7216054</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F142">
+      <c r="H142">
         <v>1923</v>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="I142" t="inlineStr">
         <is>
           <t xml:space="preserve">311434528</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="K142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7131,33 +8551,43 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 13</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151141</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F143">
+      <c r="H143">
         <v>2309</v>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">311448357</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
+      <c r="K143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7181,33 +8611,43 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 13</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151141</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F144">
+      <c r="H144">
         <v>583</v>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t xml:space="preserve">311448357</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
+      <c r="K144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7231,33 +8671,43 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 13</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151141</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F145">
+      <c r="H145">
         <v>996</v>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="I145" t="inlineStr">
         <is>
           <t xml:space="preserve">311448357</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="J145" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
+      <c r="K145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7281,33 +8731,43 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 13</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151141</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F146">
+      <c r="H146">
         <v>960</v>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t xml:space="preserve">311448357</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="J146" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
+      <c r="K146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7331,33 +8791,43 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 71P</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141859</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F147">
+      <c r="H147">
         <v>262</v>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t xml:space="preserve">311454198</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="J147" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
+      <c r="K147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7381,33 +8851,43 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 71E</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141859</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F148">
+      <c r="H148">
         <v>262</v>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t xml:space="preserve">311454198</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
+      <c r="K148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7431,33 +8911,43 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 69K</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141859</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="F149">
+      <c r="H149">
         <v>262</v>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t xml:space="preserve">311454198</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
+      <c r="K149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7481,33 +8971,43 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 69F</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141859</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
         </is>
       </c>
-      <c r="F150">
+      <c r="H150">
         <v>357</v>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t xml:space="preserve">311454196</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
+      <c r="K150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7531,33 +9031,43 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 69E</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141859</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F151">
+      <c r="H151">
         <v>369</v>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t xml:space="preserve">311454197</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
+      <c r="K151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7581,33 +9091,43 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hovedgaden 79</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141547</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F152">
+      <c r="H152">
         <v>4455</v>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t xml:space="preserve">311476580</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="J152" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-11-18</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
+      <c r="K152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7631,33 +9151,43 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørreport 4B</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
           <t xml:space="preserve">7140689</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F153">
+      <c r="H153">
         <v>2275</v>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t xml:space="preserve">311551853</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="J153" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
+      <c r="K153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7681,33 +9211,43 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørreport 4A</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
           <t xml:space="preserve">7140689</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F154">
+      <c r="H154">
         <v>1016</v>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t xml:space="preserve">311551603</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="J154" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
+      <c r="K154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7731,33 +9271,43 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørreport 4D</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
           <t xml:space="preserve">7140689</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F155">
+      <c r="H155">
         <v>553</v>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="I155" t="inlineStr">
         <is>
           <t xml:space="preserve">311551854</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="J155" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
+      <c r="K155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7781,33 +9331,43 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørreport 4G</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
           <t xml:space="preserve">7140689</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F156">
+      <c r="H156">
         <v>438</v>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t xml:space="preserve">311551855</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="J156" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
+      <c r="K156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7831,33 +9391,43 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østeralle 19</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
           <t xml:space="preserve">5617696</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F157">
+      <c r="H157">
         <v>6275</v>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="I157" t="inlineStr">
         <is>
           <t xml:space="preserve">311630904</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="J157" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-09-26</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
+      <c r="K157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7881,33 +9451,43 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F158">
+      <c r="H158">
         <v>624</v>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="I158" t="inlineStr">
         <is>
           <t xml:space="preserve">311654004</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="J158" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
+      <c r="K158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7931,33 +9511,43 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ballesvej 6</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8543</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
           <t xml:space="preserve">4148552</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F159">
+      <c r="H159">
         <v>832</v>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="I159" t="inlineStr">
         <is>
           <t xml:space="preserve">311657185</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="J159" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
+      <c r="K159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7981,33 +9571,43 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t xml:space="preserve">A. Knudsens Vej 6</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8400</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
           <t xml:space="preserve">5618869</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F160">
+      <c r="H160">
         <v>510</v>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="I160" t="inlineStr">
         <is>
           <t xml:space="preserve">311683327</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="J160" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-05-25</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
+      <c r="K160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8031,33 +9631,43 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 13A</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8544</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
           <t xml:space="preserve">4151141</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F161">
+      <c r="H161">
         <v>1066</v>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t xml:space="preserve">311700070</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="J161" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-08-15</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
+      <c r="K161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8081,33 +9691,43 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lerbakken 21</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8410</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
           <t xml:space="preserve">4141156</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F162">
+      <c r="H162">
         <v>629</v>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t xml:space="preserve">311812521</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="J162" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-19</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
+      <c r="K162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8131,33 +9751,43 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fiskegårdevej 3B</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8444</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173743</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F163">
+      <c r="H163">
         <v>890</v>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t xml:space="preserve">311812524</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="J163" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-19</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
+      <c r="K163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8181,39 +9811,49 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fiskegårdevej 3A</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8444</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
           <t xml:space="preserve">4173743</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F164">
+      <c r="H164">
         <v>753</v>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t xml:space="preserve">311812523</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="J164" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-02-19</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
+      <c r="K164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J164"/>
+  <autoFilter ref="A1:L164"/>
 </worksheet>
 </file>
--- a/public/exports/29189978.xlsx
+++ b/public/exports/29189978.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 13D</t>
+          <t xml:space="preserve">Amaliegårdvej 23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100168061</t>
+          <t xml:space="preserve">9858040</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H2">
-        <v>699</v>
+        <v>260</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,17 +151,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 13B</t>
+          <t xml:space="preserve">Bagvænget 12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100168061</t>
+          <t xml:space="preserve">9926307</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>2103</v>
+        <v>769</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandballevej 5</t>
+          <t xml:space="preserve">Ballesvej 6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033354</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H4">
-        <v>274</v>
+        <v>441</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 58</t>
+          <t xml:space="preserve">Ballesvej 6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100465851</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H5">
-        <v>1030</v>
+        <v>441</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 10</t>
+          <t xml:space="preserve">Bispemosevej 5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8444</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100625342</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H6">
-        <v>804</v>
+        <v>580</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 4A</t>
+          <t xml:space="preserve">Bispemosevej 5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8444</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">101001610, 101001611</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H7">
-        <v>4075</v>
+        <v>1267</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 15</t>
+          <t xml:space="preserve">Brunmosevej 3B</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10136366</t>
+          <t xml:space="preserve">741662, 4123842</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H8">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 17</t>
+          <t xml:space="preserve">Brunmosevej 3C</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">10136366</t>
+          <t xml:space="preserve">741663, 4123842</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>547</v>
+        <v>1540</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 19</t>
+          <t xml:space="preserve">Bugtrupvej 27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">10136366</t>
+          <t xml:space="preserve">4173780</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H10">
-        <v>450</v>
+        <v>1130</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindebo 1</t>
+          <t xml:space="preserve">Drosselvej 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">353477, 353478</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H11">
-        <v>815</v>
+        <v>766</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,17 +691,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 10</t>
+          <t xml:space="preserve">Ebdrupvej 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">361636</t>
+          <t xml:space="preserve">741661, 4174515</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="H12">
-        <v>258</v>
+        <v>550</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 10</t>
+          <t xml:space="preserve">Ebdrupvej 10A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">361636, 361638, 361639</t>
+          <t xml:space="preserve">374028, 374029</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>323</v>
+        <v>712</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ebdrupvej 10A</t>
+          <t xml:space="preserve">Egedalsvej 11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">374028, 374029</t>
+          <t xml:space="preserve">5618905</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H14">
-        <v>712</v>
+        <v>416</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 2</t>
+          <t xml:space="preserve">Egedalsvej 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">375845, 375846, 375847, 375848</t>
+          <t xml:space="preserve">8708759</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H15">
-        <v>1260</v>
+        <v>264</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,17 +931,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 30A</t>
+          <t xml:space="preserve">Engvej 18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">375855, 375856</t>
+          <t xml:space="preserve">4174148</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>666</v>
+        <v>1225</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,17 +991,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pollen 2</t>
+          <t xml:space="preserve">Falcksvej 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4117377</t>
+          <t xml:space="preserve">5619216</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="H17">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 9B</t>
+          <t xml:space="preserve">Falcksvej 4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141177</t>
+          <t xml:space="preserve">5619162</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H18">
-        <v>3262</v>
+        <v>584</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballesvej 6</t>
+          <t xml:space="preserve">Gråskegårdevej 2B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">9154991</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>441</v>
+        <v>948</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballesvej 6</t>
+          <t xml:space="preserve">Industrivej 21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">8925031</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>441</v>
+        <v>1047</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispemosevej 5</t>
+          <t xml:space="preserve">Lyngevej 7O</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">8444</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">8124496</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H22">
-        <v>580</v>
+        <v>490</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispemosevej 5</t>
+          <t xml:space="preserve">Marienhoffvej 13B</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8444</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">100168061</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H23">
-        <v>1267</v>
+        <v>2103</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 27</t>
+          <t xml:space="preserve">Marienhoffvej 13C</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173780</t>
+          <t xml:space="preserve">741660, 100168061</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H24">
-        <v>1130</v>
+        <v>833</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,26 +1471,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 18</t>
+          <t xml:space="preserve">Marienhoffvej 13D</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4174148</t>
+          <t xml:space="preserve">100168061</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H25">
-        <v>1225</v>
+        <v>699</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 8</t>
+          <t xml:space="preserve">Nørrealle 4B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617299</t>
+          <t xml:space="preserve">5617732</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>439</v>
+        <v>330</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,26 +1591,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 3</t>
+          <t xml:space="preserve">Pollen 2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617326</t>
+          <t xml:space="preserve">4117377</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>374</v>
+        <v>300</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,26 +1651,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrealle 4B</t>
+          <t xml:space="preserve">Rodskovvej 58</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617732</t>
+          <t xml:space="preserve">100465851</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H28">
-        <v>330</v>
+        <v>1030</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalsvej 11</t>
+          <t xml:space="preserve">S.A. Jensens Vej 3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618905</t>
+          <t xml:space="preserve">5617326</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H29">
-        <v>416</v>
+        <v>374</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falcksvej 4</t>
+          <t xml:space="preserve">S.A. Jensens Vej 4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619162</t>
+          <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="H30">
-        <v>584</v>
+        <v>320</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falcksvej 1</t>
+          <t xml:space="preserve">S.A. Jensens Vej 4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,16 +1841,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619216</t>
+          <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H31">
-        <v>397</v>
+        <v>1142</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 13B</t>
+          <t xml:space="preserve">S.A. Jensens Vej 4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">741593, 10136366</t>
+          <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H32">
-        <v>253</v>
+        <v>1930</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 12</t>
+          <t xml:space="preserve">Sandballevej 5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">741594, 9787579</t>
+          <t xml:space="preserve">10033354</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H33">
-        <v>500</v>
+        <v>274</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 4</t>
+          <t xml:space="preserve">Skolevej 10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,16 +2021,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">741623, 5617339</t>
+          <t xml:space="preserve">100625342</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H34">
-        <v>320</v>
+        <v>804</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 4</t>
+          <t xml:space="preserve">Skolevej 12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">741623, 5617339</t>
+          <t xml:space="preserve">8587308</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>1142</v>
+        <v>1111</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 4</t>
+          <t xml:space="preserve">Skovbakkevej 15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">741623, 5617339</t>
+          <t xml:space="preserve">741676, 4123019</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>1930</v>
+        <v>425</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skudehavnen 2B</t>
+          <t xml:space="preserve">Skrejrupvej 9B</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">741658, 10136366</t>
+          <t xml:space="preserve">4141177</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H37">
-        <v>358</v>
+        <v>3262</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 13C</t>
+          <t xml:space="preserve">Skudehavnen 2B</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">741660, 100168061</t>
+          <t xml:space="preserve">741658, 10136366</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H38">
-        <v>833</v>
+        <v>358</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ebdrupvej 1</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">741661, 4174515</t>
+          <t xml:space="preserve">7811024</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H39">
-        <v>550</v>
+        <v>254</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brunmosevej 3B</t>
+          <t xml:space="preserve">Stadionvej 4A</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">741662, 4123842</t>
+          <t xml:space="preserve">101001610, 101001611</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>401</v>
+        <v>4075</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,26 +2431,26 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brunmosevej 3C</t>
+          <t xml:space="preserve">Stockflethsvej 12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">741663, 4123842</t>
+          <t xml:space="preserve">741594, 9787579</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H41">
-        <v>1540</v>
+        <v>500</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 2B</t>
+          <t xml:space="preserve">Stockflethsvej 13B</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">741674, 4126345</t>
+          <t xml:space="preserve">741593, 10136366</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H42">
-        <v>1893</v>
+        <v>253</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,26 +2551,26 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbakkevej 15</t>
+          <t xml:space="preserve">Strandvejen 8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">741676, 4123019</t>
+          <t xml:space="preserve">5617299</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H43">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,26 +2611,26 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 1</t>
+          <t xml:space="preserve">Vestervej 15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">10136366</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H44">
-        <v>766</v>
+        <v>376</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,26 +2671,26 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Vestervej 17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7811024</t>
+          <t xml:space="preserve">10136366</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H45">
-        <v>254</v>
+        <v>547</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 7O</t>
+          <t xml:space="preserve">Vestervej 19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124496</t>
+          <t xml:space="preserve">10136366</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H46">
-        <v>490</v>
+        <v>450</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,26 +2791,26 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12</t>
+          <t xml:space="preserve">Ådalen 2B</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8587308</t>
+          <t xml:space="preserve">741674, 4126345</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H47">
-        <v>1111</v>
+        <v>1893</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,26 +2851,26 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalsvej 3</t>
+          <t xml:space="preserve">Ågårdvej 2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708759</t>
+          <t xml:space="preserve">9888746</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H48">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,17 +2911,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 21</t>
+          <t xml:space="preserve">Dråbyvej 9</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925031</t>
+          <t xml:space="preserve">9766554</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,21 +2930,21 @@
         </is>
       </c>
       <c r="H49">
-        <v>1047</v>
+        <v>265</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100132095</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråskegårdevej 2B</t>
+          <t xml:space="preserve">Lerbakken 9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9154991</t>
+          <t xml:space="preserve">4141141</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,21 +2990,21 @@
         </is>
       </c>
       <c r="H50">
-        <v>948</v>
+        <v>633</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020792</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3031,40 +3031,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amaliegårdvej 23</t>
+          <t xml:space="preserve">Bugtrupvej 33</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9858040</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H51">
-        <v>260</v>
+        <v>2569</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200041449</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-11-21</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3091,40 +3091,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdvej 2</t>
+          <t xml:space="preserve">Skovalleen 1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888746</t>
+          <t xml:space="preserve">741584, 5619151</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H52">
-        <v>309</v>
+        <v>865</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047752</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-07</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3151,40 +3151,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagvænget 12</t>
+          <t xml:space="preserve">Drosselvej 1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926307</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>769</v>
+        <v>1160</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310034752</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3211,35 +3211,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dråbyvej 9</t>
+          <t xml:space="preserve">Drosselvej 1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9766554</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H54">
-        <v>265</v>
+        <v>393</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">100132095</t>
+          <t xml:space="preserve">310034752</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-28</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbakken 9</t>
+          <t xml:space="preserve">Drosselvej 1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141141</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H55">
-        <v>633</v>
+        <v>737</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020792</t>
+          <t xml:space="preserve">310034752</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,35 +3331,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 33</t>
+          <t xml:space="preserve">Tendrup Hovvej 7A</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">100016008</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>2569</v>
+        <v>551</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041449</t>
+          <t xml:space="preserve">311002109</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-21</t>
+          <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovalleen 1</t>
+          <t xml:space="preserve">Østeralle 33</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,25 +3401,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">741584, 5619151</t>
+          <t xml:space="preserve">100064534</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H57">
-        <v>865</v>
+        <v>625</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047752</t>
+          <t xml:space="preserve">311088576</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-07</t>
+          <t xml:space="preserve">2024-12-17</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 1</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">4123748</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,26 +3470,26 @@
         </is>
       </c>
       <c r="H58">
-        <v>1160</v>
+        <v>1763</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034752</t>
+          <t xml:space="preserve">311199997</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-12</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3511,45 +3511,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 1</t>
+          <t xml:space="preserve">Egedalsvej 7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">5618905</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H59">
-        <v>393</v>
+        <v>606</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034752</t>
+          <t xml:space="preserve">311212792</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-12</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3571,45 +3571,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 1</t>
+          <t xml:space="preserve">Hovedgaden 10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">361636</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H60">
-        <v>737</v>
+        <v>258</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034752</t>
+          <t xml:space="preserve">311212799</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-12</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3631,45 +3631,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tendrup Hovvej 7A</t>
+          <t xml:space="preserve">Hovedgaden 10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">100016008</t>
+          <t xml:space="preserve">361636, 361638, 361639</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H61">
-        <v>551</v>
+        <v>323</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311002109</t>
+          <t xml:space="preserve">311212802</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-05</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 33</t>
+          <t xml:space="preserve">Hyrdebakken 2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064534</t>
+          <t xml:space="preserve">8034374</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,26 +3710,26 @@
         </is>
       </c>
       <c r="H62">
-        <v>625</v>
+        <v>461</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311088576</t>
+          <t xml:space="preserve">311212953</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-17</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Moesbakken 2A</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123748</t>
+          <t xml:space="preserve">8587307</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="H63">
-        <v>1763</v>
+        <v>445</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199997</t>
+          <t xml:space="preserve">311215580</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-12-01</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalsvej 7</t>
+          <t xml:space="preserve">Poppelvej 9</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618905</t>
+          <t xml:space="preserve">4124588</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3830,16 +3830,16 @@
         </is>
       </c>
       <c r="H64">
-        <v>606</v>
+        <v>364</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212792</t>
+          <t xml:space="preserve">311216521</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-12-07</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,17 +3871,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdebakken 2</t>
+          <t xml:space="preserve">Nordre Ringvej 5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8034374</t>
+          <t xml:space="preserve">4125011</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="H65">
-        <v>461</v>
+        <v>605</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212953</t>
+          <t xml:space="preserve">311216854</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moesbakken 2A</t>
+          <t xml:space="preserve">Falcksvej 2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8587307</t>
+          <t xml:space="preserve">4148336</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,16 +3950,16 @@
         </is>
       </c>
       <c r="H66">
-        <v>445</v>
+        <v>757</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215580</t>
+          <t xml:space="preserve">311218178</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-01</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 9</t>
+          <t xml:space="preserve">Bøgevej 1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124588</t>
+          <t xml:space="preserve">4123772</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>364</v>
+        <v>445</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216521</t>
+          <t xml:space="preserve">311219438</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-07</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 5</t>
+          <t xml:space="preserve">Eskerodvej 5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4125011</t>
+          <t xml:space="preserve">4148280</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="H68">
-        <v>605</v>
+        <v>521</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216854</t>
+          <t xml:space="preserve">311219420</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falcksvej 2</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148336</t>
+          <t xml:space="preserve">7811024</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="H69">
-        <v>757</v>
+        <v>492</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218178</t>
+          <t xml:space="preserve">311219423</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgevej 1</t>
+          <t xml:space="preserve">Ågårdvej 3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123772</t>
+          <t xml:space="preserve">9516512</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,11 +4190,11 @@
         </is>
       </c>
       <c r="H70">
-        <v>445</v>
+        <v>529</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219438</t>
+          <t xml:space="preserve">311219452</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskerodvej 5</t>
+          <t xml:space="preserve">Dalgårdsvej 2A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148280</t>
+          <t xml:space="preserve">4155496</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>521</v>
+        <v>353</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219420</t>
+          <t xml:space="preserve">311231282</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Alpedalen 14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7811024</t>
+          <t xml:space="preserve">4149074</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>492</v>
+        <v>389</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219423</t>
+          <t xml:space="preserve">311249201</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdvej 3</t>
+          <t xml:space="preserve">Egedalsvej 2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9516512</t>
+          <t xml:space="preserve">5618867</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,16 +4370,16 @@
         </is>
       </c>
       <c r="H73">
-        <v>529</v>
+        <v>769</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219452</t>
+          <t xml:space="preserve">311250893</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgårdsvej 2A</t>
+          <t xml:space="preserve">Bagvænget 12</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155496</t>
+          <t xml:space="preserve">9926307</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>353</v>
+        <v>2200</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231282</t>
+          <t xml:space="preserve">311253872</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-01</t>
+          <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alpedalen 14</t>
+          <t xml:space="preserve">Bugtrupvej 27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4149074</t>
+          <t xml:space="preserve">4173991</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>389</v>
+        <v>6272</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249201</t>
+          <t xml:space="preserve">311253826</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,35 +4531,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalsvej 2</t>
+          <t xml:space="preserve">Bugtrupvej 27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618867</t>
+          <t xml:space="preserve">4173991</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H76">
-        <v>769</v>
+        <v>787</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250893</t>
+          <t xml:space="preserve">311253826</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 27</t>
+          <t xml:space="preserve">Strandgårdshøj 46A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173991</t>
+          <t xml:space="preserve">5618735</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,11 +4610,11 @@
         </is>
       </c>
       <c r="H77">
-        <v>6272</v>
+        <v>672</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253826</t>
+          <t xml:space="preserve">311253843</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4651,30 +4651,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 27</t>
+          <t xml:space="preserve">Vestervej 7</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173991</t>
+          <t xml:space="preserve">9926304</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H78">
-        <v>787</v>
+        <v>1282</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253826</t>
+          <t xml:space="preserve">311253876</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgårdshøj 46A</t>
+          <t xml:space="preserve">Rosenholmvej 1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618735</t>
+          <t xml:space="preserve">4148297</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,16 +4730,16 @@
         </is>
       </c>
       <c r="H79">
-        <v>672</v>
+        <v>1174</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253843</t>
+          <t xml:space="preserve">311254476</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-14</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 7</t>
+          <t xml:space="preserve">Nyvej 3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926304</t>
+          <t xml:space="preserve">4148947</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>1282</v>
+        <v>715</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253876</t>
+          <t xml:space="preserve">311258642</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-14</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagvænget 12</t>
+          <t xml:space="preserve">Strandvejen 8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926307</t>
+          <t xml:space="preserve">5617299</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="H81">
-        <v>2200</v>
+        <v>628</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253872</t>
+          <t xml:space="preserve">311258644</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-14</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 1</t>
+          <t xml:space="preserve">Østeralle 17A</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148297</t>
+          <t xml:space="preserve">5617697</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>1174</v>
+        <v>1675</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254476</t>
+          <t xml:space="preserve">311258643</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 3</t>
+          <t xml:space="preserve">Mosevej 9</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148947</t>
+          <t xml:space="preserve">4151345</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>715</v>
+        <v>851</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258642</t>
+          <t xml:space="preserve">311258719</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 8</t>
+          <t xml:space="preserve">Vestergade 116A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617299</t>
+          <t xml:space="preserve">4123336</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="H84">
-        <v>628</v>
+        <v>970</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258644</t>
+          <t xml:space="preserve">311258741</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 17A</t>
+          <t xml:space="preserve">Engvej 24A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617697</t>
+          <t xml:space="preserve">4149546</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="H85">
-        <v>1675</v>
+        <v>275</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258643</t>
+          <t xml:space="preserve">311280697</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-10-26</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 116A</t>
+          <t xml:space="preserve">Bispemosevej 5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8444</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123336</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>970</v>
+        <v>5211</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258741</t>
+          <t xml:space="preserve">311287373</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 9</t>
+          <t xml:space="preserve">S.A. Jensens Vej 1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151345</t>
+          <t xml:space="preserve">5617328</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>851</v>
+        <v>722</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258719</t>
+          <t xml:space="preserve">311291350</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 24A</t>
+          <t xml:space="preserve">Maarupvej 3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4149546</t>
+          <t xml:space="preserve">4174157</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H88">
-        <v>275</v>
+        <v>1503</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280697</t>
+          <t xml:space="preserve">311293050</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-26</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispemosevej 5</t>
+          <t xml:space="preserve">Kløvervangen 6A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8444</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">4155954</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,16 +5330,16 @@
         </is>
       </c>
       <c r="H89">
-        <v>5211</v>
+        <v>576</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287373</t>
+          <t xml:space="preserve">311294468</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 1</t>
+          <t xml:space="preserve">Kløvervangen 6A</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617328</t>
+          <t xml:space="preserve">4155954</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H90">
-        <v>722</v>
+        <v>2481</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291350</t>
+          <t xml:space="preserve">311294468</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maarupvej 3</t>
+          <t xml:space="preserve">Kløvervangen 6A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4174157</t>
+          <t xml:space="preserve">4155954</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H91">
-        <v>1503</v>
+        <v>365</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293050</t>
+          <t xml:space="preserve">311294468</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,30 +5491,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 17</t>
+          <t xml:space="preserve">Kløvervangen 6B</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148745</t>
+          <t xml:space="preserve">4155954</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H92">
-        <v>3923</v>
+        <v>1214</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294457</t>
+          <t xml:space="preserve">311294471</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,17 +5551,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervangen 6A</t>
+          <t xml:space="preserve">Tingvej 17</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155954</t>
+          <t xml:space="preserve">4148745</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5570,11 +5570,11 @@
         </is>
       </c>
       <c r="H93">
-        <v>576</v>
+        <v>3923</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294468</t>
+          <t xml:space="preserve">311294457</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervangen 6A</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155954</t>
+          <t xml:space="preserve">5617617</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H94">
-        <v>2481</v>
+        <v>7166</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294468</t>
+          <t xml:space="preserve">311294654</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-25</t>
+          <t xml:space="preserve">2028-01-26</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,35 +5671,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervangen 6B</t>
+          <t xml:space="preserve">Lyngevej 3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155954</t>
+          <t xml:space="preserve">8708462</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H95">
-        <v>1214</v>
+        <v>1466</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294470</t>
+          <t xml:space="preserve">311296511</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-25</t>
+          <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,35 +5731,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervangen 6A</t>
+          <t xml:space="preserve">Lyngevej 7</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155954</t>
+          <t xml:space="preserve">8124496</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H96">
-        <v>365</v>
+        <v>490</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294468</t>
+          <t xml:space="preserve">311296510</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-25</t>
+          <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Lyngevej 7H</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617617</t>
+          <t xml:space="preserve">8124496</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H97">
-        <v>7166</v>
+        <v>490</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294654</t>
+          <t xml:space="preserve">311296510</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-26</t>
+          <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 7</t>
+          <t xml:space="preserve">Skrejrupvej 1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124496</t>
+          <t xml:space="preserve">4141159</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H101">
-        <v>490</v>
+        <v>2122</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296510</t>
+          <t xml:space="preserve">311299126</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-07</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 7H</t>
+          <t xml:space="preserve">Skrejrupvej 1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124496</t>
+          <t xml:space="preserve">4141159</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H102">
-        <v>490</v>
+        <v>640</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296510</t>
+          <t xml:space="preserve">311299126</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-07</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 3</t>
+          <t xml:space="preserve">Skrejrupvej 1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708462</t>
+          <t xml:space="preserve">4141159</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H103">
-        <v>1466</v>
+        <v>2258</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296511</t>
+          <t xml:space="preserve">311299126</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-07</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6226,11 +6226,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H104">
-        <v>2122</v>
+        <v>3414</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6286,11 +6286,11 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H105">
-        <v>640</v>
+        <v>703</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 1</t>
+          <t xml:space="preserve">Skrejrupvej 7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6346,11 +6346,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H106">
-        <v>2258</v>
+        <v>691</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6391,35 +6391,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 1</t>
+          <t xml:space="preserve">Skolevej 19</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141159</t>
+          <t xml:space="preserve">4151491</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H107">
-        <v>3414</v>
+        <v>865</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299126</t>
+          <t xml:space="preserve">311330686</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,35 +6451,35 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 1</t>
+          <t xml:space="preserve">Nørreport 18A</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141159</t>
+          <t xml:space="preserve">5618817</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>703</v>
+        <v>1294</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299126</t>
+          <t xml:space="preserve">311332828</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-08-28</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,35 +6511,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 7</t>
+          <t xml:space="preserve">Lundbergsvej 2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141159</t>
+          <t xml:space="preserve">5618414</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H109">
-        <v>691</v>
+        <v>9380</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299126</t>
+          <t xml:space="preserve">311339427</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,35 +6571,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 19</t>
+          <t xml:space="preserve">Nordre Ringvej 7A</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151491</t>
+          <t xml:space="preserve">4124942</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>865</v>
+        <v>430</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330686</t>
+          <t xml:space="preserve">311339459</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-15</t>
+          <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 18A</t>
+          <t xml:space="preserve">Rosengården 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618817</t>
+          <t xml:space="preserve">7205819</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="H111">
-        <v>1294</v>
+        <v>2019</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332828</t>
+          <t xml:space="preserve">311340763</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-28</t>
+          <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,35 +6691,35 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 7A</t>
+          <t xml:space="preserve">Rosengården 1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124942</t>
+          <t xml:space="preserve">7205819</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H112">
-        <v>430</v>
+        <v>6224</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339459</t>
+          <t xml:space="preserve">311340762</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-03</t>
+          <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,35 +6751,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbergsvej 2</t>
+          <t xml:space="preserve">Kløvevej 1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618414</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H113">
-        <v>9380</v>
+        <v>875</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339427</t>
+          <t xml:space="preserve">311344086</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-03</t>
+          <t xml:space="preserve">2028-10-30</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosengården 1</t>
+          <t xml:space="preserve">Skoletoften 17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205819</t>
+          <t xml:space="preserve">4165334</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6830,16 +6830,16 @@
         </is>
       </c>
       <c r="H114">
-        <v>2019</v>
+        <v>4960</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340763</t>
+          <t xml:space="preserve">311347460</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-10</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosengården 1</t>
+          <t xml:space="preserve">Skoletoften 17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205819</t>
+          <t xml:space="preserve">4165334</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="H115">
-        <v>6224</v>
+        <v>779</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340765</t>
+          <t xml:space="preserve">311347460</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-10</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,35 +6931,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvevej 1</t>
+          <t xml:space="preserve">Bugtrupvej 29</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>875</v>
+        <v>480</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344086</t>
+          <t xml:space="preserve">311352227</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-30</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,35 +6991,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 17</t>
+          <t xml:space="preserve">Bugtrupvej 29</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165334</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H117">
-        <v>4960</v>
+        <v>523</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347460</t>
+          <t xml:space="preserve">311352227</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,35 +7051,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 17</t>
+          <t xml:space="preserve">Ådalen 2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165334</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H118">
-        <v>779</v>
+        <v>2790</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347460</t>
+          <t xml:space="preserve">311354232</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,35 +7111,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 29</t>
+          <t xml:space="preserve">Ådalen 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H119">
-        <v>480</v>
+        <v>2973</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352227</t>
+          <t xml:space="preserve">311354232</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,35 +7171,35 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 29</t>
+          <t xml:space="preserve">Ballesvej 6</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>523</v>
+        <v>3597</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352227</t>
+          <t xml:space="preserve">311358653</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 2</t>
+          <t xml:space="preserve">Ballesvej 6</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H121">
-        <v>2790</v>
+        <v>4680</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354232</t>
+          <t xml:space="preserve">311358653</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-10</t>
+          <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 2</t>
+          <t xml:space="preserve">Ballesvej 6</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H122">
-        <v>2973</v>
+        <v>667</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354232</t>
+          <t xml:space="preserve">311358653</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-10</t>
+          <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7366,11 +7366,11 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H123">
-        <v>3597</v>
+        <v>872</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballesvej 6</t>
+          <t xml:space="preserve">Skolevangen 1</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7426,15 +7426,15 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H124">
-        <v>4680</v>
+        <v>488</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358653</t>
+          <t xml:space="preserve">311358656</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballesvej 6</t>
+          <t xml:space="preserve">Bugtrupvej 41</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>667</v>
+        <v>1068</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358653</t>
+          <t xml:space="preserve">311364664</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-08</t>
+          <t xml:space="preserve">2029-03-14</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,35 +7531,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 1</t>
+          <t xml:space="preserve">Bugtrupvej 39</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H126">
-        <v>488</v>
+        <v>1052</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358656</t>
+          <t xml:space="preserve">311364992</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-08</t>
+          <t xml:space="preserve">2029-03-15</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballesvej 6</t>
+          <t xml:space="preserve">Rodskovvej 10A</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,25 +7601,25 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">4148190</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H127">
-        <v>872</v>
+        <v>1095</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358653</t>
+          <t xml:space="preserve">311377157</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-08</t>
+          <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 41</t>
+          <t xml:space="preserve">Rodskovvej 10B</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">4148190</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H128">
-        <v>1068</v>
+        <v>338</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311364664</t>
+          <t xml:space="preserve">311377157</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-14</t>
+          <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,35 +7711,35 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 39</t>
+          <t xml:space="preserve">Marienhoffvej 11A</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">1447910</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H129">
-        <v>1052</v>
+        <v>5629</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311364992</t>
+          <t xml:space="preserve">311412947</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-15</t>
+          <t xml:space="preserve">2029-12-09</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 10A</t>
+          <t xml:space="preserve">Lufthavnsvej 17</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148190</t>
+          <t xml:space="preserve">4171414</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>1095</v>
+        <v>464</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377157</t>
+          <t xml:space="preserve">311413089</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-15</t>
+          <t xml:space="preserve">2029-12-10</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,35 +7831,35 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 10B</t>
+          <t xml:space="preserve">Lindebo 1</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148190</t>
+          <t xml:space="preserve">353477, 353478</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H131">
-        <v>338</v>
+        <v>815</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377157</t>
+          <t xml:space="preserve">311413537</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-15</t>
+          <t xml:space="preserve">2029-12-12</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 11A</t>
+          <t xml:space="preserve">Nordre Ringvej 9K</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7901,25 +7901,25 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1447910</t>
+          <t xml:space="preserve">4124915</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H132">
-        <v>5629</v>
+        <v>2812</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412947</t>
+          <t xml:space="preserve">311417162</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-09</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lufthavnsvej 17</t>
+          <t xml:space="preserve">Århusvej 33H</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171414</t>
+          <t xml:space="preserve">1803816</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H133">
-        <v>464</v>
+        <v>360</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311413089</t>
+          <t xml:space="preserve">311417751</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-10</t>
+          <t xml:space="preserve">2030-01-17</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,35 +8011,35 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 9K</t>
+          <t xml:space="preserve">Bakkevej 5A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124915</t>
+          <t xml:space="preserve">5618818</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H134">
-        <v>2812</v>
+        <v>1422</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417162</t>
+          <t xml:space="preserve">311418867</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 33H</t>
+          <t xml:space="preserve">Nørreport 20A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803816</t>
+          <t xml:space="preserve">8496559</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>360</v>
+        <v>728</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417751</t>
+          <t xml:space="preserve">311419346</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-17</t>
+          <t xml:space="preserve">2030-01-28</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,17 +8131,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 5A</t>
+          <t xml:space="preserve">Bugtrupvej 35A</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618818</t>
+          <t xml:space="preserve">7961824</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8150,16 +8150,16 @@
         </is>
       </c>
       <c r="H136">
-        <v>1422</v>
+        <v>725</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418867</t>
+          <t xml:space="preserve">311420125</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 20A</t>
+          <t xml:space="preserve">Bugtrupvej 37</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8496559</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="H137">
-        <v>728</v>
+        <v>453</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419346</t>
+          <t xml:space="preserve">311420126</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-28</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,35 +8251,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 37</t>
+          <t xml:space="preserve">Lyngevej 5R</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">8708462</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H138">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420126</t>
+          <t xml:space="preserve">311422782</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-02-14</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,35 +8311,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 35A</t>
+          <t xml:space="preserve">Hovedgaden 75A</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961824</t>
+          <t xml:space="preserve">7216054</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H139">
-        <v>725</v>
+        <v>1923</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420125</t>
+          <t xml:space="preserve">311434528</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,35 +8371,35 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5R</t>
+          <t xml:space="preserve">Hovedgaden 77</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708462</t>
+          <t xml:space="preserve">7216054</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H140">
-        <v>480</v>
+        <v>3084</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422782</t>
+          <t xml:space="preserve">311424218</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-14</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,35 +8431,35 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 77</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7216054</t>
+          <t xml:space="preserve">4151141</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H141">
-        <v>3084</v>
+        <v>2309</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424218</t>
+          <t xml:space="preserve">311448357</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,35 +8491,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 75A</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7216054</t>
+          <t xml:space="preserve">4151141</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H142">
-        <v>1923</v>
+        <v>583</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311434528</t>
+          <t xml:space="preserve">311448357</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8566,11 +8566,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H143">
-        <v>2309</v>
+        <v>996</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H144">
-        <v>583</v>
+        <v>960</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -8671,35 +8671,35 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Hovedgaden 69E</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151141</t>
+          <t xml:space="preserve">4141859</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H145">
-        <v>996</v>
+        <v>369</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448357</t>
+          <t xml:space="preserve">311454197</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-07</t>
+          <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,35 +8731,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Hovedgaden 69F</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151141</t>
+          <t xml:space="preserve">4141859</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="H146">
-        <v>960</v>
+        <v>357</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448357</t>
+          <t xml:space="preserve">311454196</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-07</t>
+          <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 71P</t>
+          <t xml:space="preserve">Hovedgaden 69K</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H147">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69K</t>
+          <t xml:space="preserve">Hovedgaden 71P</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H149">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69F</t>
+          <t xml:space="preserve">Hovedgaden 79</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141859</t>
+          <t xml:space="preserve">4141547</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H150">
-        <v>357</v>
+        <v>4455</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454196</t>
+          <t xml:space="preserve">311476580</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-13</t>
+          <t xml:space="preserve">2030-11-18</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,35 +9031,35 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69E</t>
+          <t xml:space="preserve">Kirkegade 30A</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141859</t>
+          <t xml:space="preserve">375855, 375856</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>369</v>
+        <v>666</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454197</t>
+          <t xml:space="preserve">311551602</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-13</t>
+          <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,17 +9091,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 79</t>
+          <t xml:space="preserve">Nørreport 4A</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141547</t>
+          <t xml:space="preserve">7140689</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9110,16 +9110,16 @@
         </is>
       </c>
       <c r="H152">
-        <v>4455</v>
+        <v>1016</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476580</t>
+          <t xml:space="preserve">311551603</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-18</t>
+          <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 4A</t>
+          <t xml:space="preserve">Nørreport 4D</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9226,15 +9226,15 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H154">
-        <v>1016</v>
+        <v>553</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551603</t>
+          <t xml:space="preserve">311551854</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 4D</t>
+          <t xml:space="preserve">Nørreport 4G</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9286,15 +9286,15 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H155">
-        <v>553</v>
+        <v>438</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551854</t>
+          <t xml:space="preserve">311551855</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 4G</t>
+          <t xml:space="preserve">Nørreport 2</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,25 +9341,25 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7140689</t>
+          <t xml:space="preserve">375845, 375846, 375847, 375848</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H156">
-        <v>438</v>
+        <v>1260</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551855</t>
+          <t xml:space="preserve">311561556</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-29</t>
+          <t xml:space="preserve">2031-11-12</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9691,30 +9691,30 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbakken 21</t>
+          <t xml:space="preserve">Fiskegårdevej 3A</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8444</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141156</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H162">
-        <v>629</v>
+        <v>753</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812521</t>
+          <t xml:space="preserve">311812523</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9811,30 +9811,30 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiskegårdevej 3A</t>
+          <t xml:space="preserve">Lerbakken 21</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8444</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">4141156</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>753</v>
+        <v>629</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812523</t>
+          <t xml:space="preserve">311812521</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">

--- a/public/exports/29189978.xlsx
+++ b/public/exports/29189978.xlsx
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294471</t>
+          <t xml:space="preserve">311294470</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">

--- a/public/exports/29189978.xlsx
+++ b/public/exports/29189978.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:M164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-21</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Korsbæk &amp; Partnere Rådgivende ingeniørfirma KS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-07</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kuben Management A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kuben Management A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kuben Management A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Murbyg ApS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-12-17</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-01</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-07</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-26</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-26</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-28</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-30</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S Rådgivende Ingeniørfirma</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-14</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S Rådgivende Ingeniørfirma</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-15</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-09</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-10</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-12</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-17</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-28</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-14</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-18</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-12</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Murbyg ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-26</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-25</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-15</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-19</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-19</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,21 +10654,26 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-19</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L164"/>
+  <autoFilter ref="A1:M164"/>
 </worksheet>
 </file>